--- a/Employee_Reports_wi52/Jeffrey Manarpaac Urolaza Q0503.xlsx
+++ b/Employee_Reports_wi52/Jeffrey Manarpaac Urolaza Q0503.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1390,11 +1390,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1439,11 +1439,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1537,11 +1537,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1586,11 +1586,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1635,11 +1635,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1684,11 +1684,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1880,11 +1880,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1929,11 +1929,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1978,11 +1978,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2027,11 +2027,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2076,11 +2076,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2125,11 +2125,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2174,11 +2174,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2211,11 +2211,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2260,11 +2260,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2309,11 +2309,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2346,11 +2346,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2395,11 +2395,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-155</v>
+        <v>-163</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2444,11 +2444,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2493,11 +2493,11 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-155</v>
+        <v>-163</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2542,11 +2542,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2640,11 +2640,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2689,11 +2689,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2726,11 +2726,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -2775,11 +2775,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -2812,11 +2812,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7776</v>
+        <v>7768</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
